--- a/proposals/CZ設計パターン一覧.xlsx
+++ b/proposals/CZ設計パターン一覧.xlsx
@@ -20,7 +20,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="6">
+  <fonts count="7">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -55,8 +55,12 @@
       <color rgb="00FFFFFF"/>
       <sz val="9"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+    </font>
   </fonts>
-  <fills count="22">
+  <fills count="25">
     <fill>
       <patternFill/>
     </fill>
@@ -161,6 +165,24 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00F2F3F4"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="004472C4"/>
+        <bgColor rgb="004472C4"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFCCCC"/>
+        <bgColor rgb="00FFCCCC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFFCC"/>
+        <bgColor rgb="00FFFFCC"/>
       </patternFill>
     </fill>
   </fills>
@@ -223,7 +245,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="60">
+  <cellXfs count="68">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -392,6 +414,30 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="21" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="22" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="23" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="23" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="23" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="23" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="23" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="24" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -759,7 +805,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H37"/>
+  <dimension ref="A1:I37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -813,6 +859,11 @@
           <t>プレイヤー体験・設計価値</t>
         </is>
       </c>
+      <c r="I1" s="60" t="inlineStr">
+        <is>
+          <t>遊技状態</t>
+        </is>
+      </c>
     </row>
     <row r="2" ht="52" customHeight="1">
       <c r="A2" s="2" t="n">
@@ -852,6 +903,11 @@
       <c r="H2" s="3" t="inlineStr">
         <is>
           <t>短期決戦の緊張感。当たるか外れるかがすぐ分かる爽快設計</t>
+        </is>
+      </c>
+      <c r="I2" s="61" t="inlineStr">
+        <is>
+          <t>CZ</t>
         </is>
       </c>
     </row>
@@ -884,6 +940,11 @@
           <t>小役を引くたびに延命できる「自分で粘れる感覚」</t>
         </is>
       </c>
+      <c r="I3" s="61" t="inlineStr">
+        <is>
+          <t>CZ</t>
+        </is>
+      </c>
     </row>
     <row r="4" ht="52" customHeight="1">
       <c r="A4" s="7" t="n"/>
@@ -912,6 +973,11 @@
       <c r="H4" s="3" t="inlineStr">
         <is>
           <t>周期到達の達成感＋レア役の偶然性が交差する設計</t>
+        </is>
+      </c>
+      <c r="I4" s="61" t="inlineStr">
+        <is>
+          <t>CZ</t>
         </is>
       </c>
     </row>
@@ -965,34 +1031,44 @@
           <t>IP愛着がある敵キャラへの「勝ちたい」感情が高揚感を生む</t>
         </is>
       </c>
+      <c r="I6" s="61" t="inlineStr">
+        <is>
+          <t>CZ</t>
+        </is>
+      </c>
     </row>
     <row r="7" ht="52" customHeight="1">
       <c r="A7" s="6" t="n"/>
       <c r="B7" s="6" t="n"/>
       <c r="C7" s="6" t="n"/>
-      <c r="D7" s="11" t="inlineStr">
+      <c r="D7" s="62" t="inlineStr">
         <is>
           <t>スマスロ 炎炎ノ消防隊2</t>
         </is>
       </c>
-      <c r="E7" s="10" t="inlineStr">
+      <c r="E7" s="63" t="inlineStr">
         <is>
           <t>炎炎激闘</t>
         </is>
       </c>
-      <c r="F7" s="12" t="inlineStr">
+      <c r="F7" s="64" t="inlineStr">
         <is>
           <t>可変</t>
         </is>
       </c>
-      <c r="G7" s="10" t="inlineStr">
+      <c r="G7" s="63" t="inlineStr">
         <is>
           <t>バトル勝利でボーナス獲得。連チャンの爽快感を重視した設計。</t>
         </is>
       </c>
-      <c r="H7" s="10" t="inlineStr">
+      <c r="H7" s="63" t="inlineStr">
         <is>
           <t>戦闘演出の迫力と当否のドキドキが一体化</t>
+        </is>
+      </c>
+      <c r="I7" s="65" t="inlineStr">
+        <is>
+          <t>AT/ボーナス（純増あり）★</t>
         </is>
       </c>
     </row>
@@ -1000,29 +1076,34 @@
       <c r="A8" s="7" t="n"/>
       <c r="B8" s="7" t="n"/>
       <c r="C8" s="7" t="n"/>
-      <c r="D8" s="11" t="inlineStr">
+      <c r="D8" s="62" t="inlineStr">
         <is>
           <t>スマスロ 東京喰種</t>
         </is>
       </c>
-      <c r="E8" s="10" t="inlineStr">
+      <c r="E8" s="63" t="inlineStr">
         <is>
           <t>バトルCZ</t>
         </is>
       </c>
-      <c r="F8" s="12" t="inlineStr">
+      <c r="F8" s="64" t="inlineStr">
         <is>
           <t>50G前後</t>
         </is>
       </c>
-      <c r="G8" s="10" t="inlineStr">
+      <c r="G8" s="63" t="inlineStr">
         <is>
           <t>対戦相手で期待度が変化。上位AT（天国）確定の可能性あり。</t>
         </is>
       </c>
-      <c r="H8" s="10" t="inlineStr">
+      <c r="H8" s="63" t="inlineStr">
         <is>
           <t>弱い相手＝ガッカリ、強い相手＝期待というIP知識が活きる設計</t>
+        </is>
+      </c>
+      <c r="I8" s="65" t="inlineStr">
+        <is>
+          <t>AT中のCZ抽選（純増あり）★</t>
         </is>
       </c>
     </row>
@@ -1037,43 +1118,48 @@
       <c r="H9" s="8" t="inlineStr"/>
     </row>
     <row r="10" ht="52" customHeight="1">
-      <c r="A10" s="13" t="n">
+      <c r="A10" s="66" t="n">
         <v>3</v>
       </c>
-      <c r="B10" s="13" t="inlineStr">
+      <c r="B10" s="66" t="inlineStr">
         <is>
           <t>セット継続型</t>
         </is>
       </c>
-      <c r="C10" s="14" t="inlineStr">
+      <c r="C10" s="63" t="inlineStr">
         <is>
           <t>1セットごとに継続/終了を抽選。
 「もう1セット」の期待で引き付ける。</t>
         </is>
       </c>
-      <c r="D10" s="15" t="inlineStr">
+      <c r="D10" s="62" t="inlineStr">
         <is>
           <t>スマスロ 革命機ヴァルヴレイヴ2</t>
         </is>
       </c>
-      <c r="E10" s="14" t="inlineStr">
+      <c r="E10" s="63" t="inlineStr">
         <is>
           <t>引き戻しゾーン</t>
         </is>
       </c>
-      <c r="F10" s="16" t="inlineStr">
+      <c r="F10" s="64" t="inlineStr">
         <is>
           <t>66G×複数セット</t>
         </is>
       </c>
-      <c r="G10" s="14" t="inlineStr">
+      <c r="G10" s="63" t="inlineStr">
         <is>
           <t>AT終了後の66G継続ゾーン。複数セット継続でAT復帰に期待。</t>
         </is>
       </c>
-      <c r="H10" s="14" t="inlineStr">
+      <c r="H10" s="63" t="inlineStr">
         <is>
           <t>終わらない期待感。「まだ終わってない」の持続設計</t>
+        </is>
+      </c>
+      <c r="I10" s="65" t="inlineStr">
+        <is>
+          <t>AT後引き戻し（純増あり）★</t>
         </is>
       </c>
     </row>
@@ -1106,34 +1192,44 @@
           <t>セットを積み上げるほど昂ぶる期待感</t>
         </is>
       </c>
+      <c r="I11" s="61" t="inlineStr">
+        <is>
+          <t>CZ（高確ループ）</t>
+        </is>
+      </c>
     </row>
     <row r="12" ht="52" customHeight="1">
       <c r="A12" s="7" t="n"/>
       <c r="B12" s="7" t="n"/>
       <c r="C12" s="7" t="n"/>
-      <c r="D12" s="15" t="inlineStr">
+      <c r="D12" s="62" t="inlineStr">
         <is>
           <t>スマスロ からくりサーカス</t>
         </is>
       </c>
-      <c r="E12" s="14" t="inlineStr">
+      <c r="E12" s="63" t="inlineStr">
         <is>
           <t>懸糸傀儡</t>
         </is>
       </c>
-      <c r="F12" s="16" t="inlineStr">
+      <c r="F12" s="64" t="inlineStr">
         <is>
           <t>3セット+</t>
         </is>
       </c>
-      <c r="G12" s="14" t="inlineStr">
+      <c r="G12" s="63" t="inlineStr">
         <is>
           <t>真夜中のサーカス突入時は3セット継続濃厚。セット消化でAT確定。</t>
         </is>
       </c>
-      <c r="H12" s="14" t="inlineStr">
+      <c r="H12" s="63" t="inlineStr">
         <is>
           <t>「3セット行ったら確定」という分かりやすいゴール設計</t>
+        </is>
+      </c>
+      <c r="I12" s="65" t="inlineStr">
+        <is>
+          <t>AT（純増あり）★</t>
         </is>
       </c>
     </row>
@@ -1187,6 +1283,11 @@
           <t>リールの出目を「読む」楽しさ。熟練者ほど興奮できる設計</t>
         </is>
       </c>
+      <c r="I14" s="61" t="inlineStr">
+        <is>
+          <t>CZ</t>
+        </is>
+      </c>
     </row>
     <row r="15" ht="52" customHeight="1">
       <c r="A15" s="6" t="n"/>
@@ -1217,6 +1318,11 @@
           <t>小役の引きが直接ダメージに変換される因果の明快さ</t>
         </is>
       </c>
+      <c r="I15" s="61" t="inlineStr">
+        <is>
+          <t>CZ</t>
+        </is>
+      </c>
     </row>
     <row r="16" ht="52" customHeight="1">
       <c r="A16" s="7" t="n"/>
@@ -1245,6 +1351,11 @@
       <c r="H16" s="18" t="inlineStr">
         <is>
           <t>押し順当ては「当たった！」の達成感が強い。ライトユーザー向け</t>
+        </is>
+      </c>
+      <c r="I16" s="61" t="inlineStr">
+        <is>
+          <t>CZ</t>
         </is>
       </c>
     </row>
@@ -1298,34 +1409,44 @@
           <t>CZを繰り返すうちに「いつか必ず当たる」という持続的期待を生む</t>
         </is>
       </c>
+      <c r="I18" s="61" t="inlineStr">
+        <is>
+          <t>CZ</t>
+        </is>
+      </c>
     </row>
     <row r="19" ht="52" customHeight="1">
       <c r="A19" s="6" t="n"/>
       <c r="B19" s="6" t="n"/>
       <c r="C19" s="6" t="n"/>
-      <c r="D19" s="23" t="inlineStr">
+      <c r="D19" s="62" t="inlineStr">
         <is>
           <t>スマスロ 鉄拳6</t>
         </is>
       </c>
-      <c r="E19" s="22" t="inlineStr">
+      <c r="E19" s="63" t="inlineStr">
         <is>
           <t>鉄拳チャンス</t>
         </is>
       </c>
-      <c r="F19" s="24" t="inlineStr">
+      <c r="F19" s="64" t="inlineStr">
         <is>
           <t>15G×繰り返し</t>
         </is>
       </c>
-      <c r="G19" s="22" t="inlineStr">
+      <c r="G19" s="63" t="inlineStr">
         <is>
           <t>15GのCZをボーナス後に繰り返し突入。拳奪バトルでボーナス継続。</t>
         </is>
       </c>
-      <c r="H19" s="22" t="inlineStr">
+      <c r="H19" s="63" t="inlineStr">
         <is>
           <t>短期CZの繰り返しが連続当選感を演出</t>
+        </is>
+      </c>
+      <c r="I19" s="65" t="inlineStr">
+        <is>
+          <t>AT中（ボーナス間・純増あり）★</t>
         </is>
       </c>
     </row>
@@ -1356,6 +1477,11 @@
       <c r="H20" s="22" t="inlineStr">
         <is>
           <t>「次の周期では当たるかも」という継続モチベーション設計</t>
+        </is>
+      </c>
+      <c r="I20" s="61" t="inlineStr">
+        <is>
+          <t>CZ</t>
         </is>
       </c>
     </row>
@@ -1409,34 +1535,44 @@
           <t>「たった3G」の極度の緊張感。終わった瞬間の逆転期待</t>
         </is>
       </c>
+      <c r="I22" s="61" t="inlineStr">
+        <is>
+          <t>AT後引き戻しCZ（純増なし）</t>
+        </is>
+      </c>
     </row>
     <row r="23" ht="52" customHeight="1">
       <c r="A23" s="6" t="n"/>
       <c r="B23" s="6" t="n"/>
       <c r="C23" s="6" t="n"/>
-      <c r="D23" s="27" t="inlineStr">
+      <c r="D23" s="62" t="inlineStr">
         <is>
           <t>スマスロ 革命機ヴァルヴレイヴ2</t>
         </is>
       </c>
-      <c r="E23" s="26" t="inlineStr">
+      <c r="E23" s="63" t="inlineStr">
         <is>
           <t>引き戻しゾーン</t>
         </is>
       </c>
-      <c r="F23" s="28" t="inlineStr">
+      <c r="F23" s="64" t="inlineStr">
         <is>
           <t>66G</t>
         </is>
       </c>
-      <c r="G23" s="26" t="inlineStr">
+      <c r="G23" s="63" t="inlineStr">
         <is>
           <t>AT終了後66G継続。紫ランプ点滅で突入示唆。</t>
         </is>
       </c>
-      <c r="H23" s="26" t="inlineStr">
+      <c r="H23" s="63" t="inlineStr">
         <is>
           <t>長めの引き戻しゾーンで「まだチャンスがある」持続感</t>
+        </is>
+      </c>
+      <c r="I23" s="65" t="inlineStr">
+        <is>
+          <t>AT後引き戻し（純増あり）★</t>
         </is>
       </c>
     </row>
@@ -1467,6 +1603,11 @@
       <c r="H24" s="26" t="inlineStr">
         <is>
           <t>「外れても損していない」というマイナスを緩和する設計</t>
+        </is>
+      </c>
+      <c r="I24" s="61" t="inlineStr">
+        <is>
+          <t>CZ失敗後システム（純増なし）</t>
         </is>
       </c>
     </row>
@@ -1520,6 +1661,11 @@
           <t>昇格のたびに期待度が上昇するRPG的な達成感</t>
         </is>
       </c>
+      <c r="I26" s="61" t="inlineStr">
+        <is>
+          <t>CZ（昇格型）</t>
+        </is>
+      </c>
     </row>
     <row r="27" ht="52" customHeight="1">
       <c r="A27" s="6" t="n"/>
@@ -1550,6 +1696,11 @@
           <t>モード昇格の瞬間が最大の興奮ポイント。段階の視覚化が重要</t>
         </is>
       </c>
+      <c r="I27" s="67" t="inlineStr">
+        <is>
+          <t>通常〜CZ（内部モード）</t>
+        </is>
+      </c>
     </row>
     <row r="28" ht="52" customHeight="1">
       <c r="A28" s="7" t="n"/>
@@ -1578,6 +1729,11 @@
       <c r="H28" s="30" t="inlineStr">
         <is>
           <t>外部から見えない内部昇格の存在が「実はもう昇格している」期待を生む</t>
+        </is>
+      </c>
+      <c r="I28" s="61" t="inlineStr">
+        <is>
+          <t>CZ→AT昇格前兆</t>
         </is>
       </c>
     </row>
@@ -1631,6 +1787,11 @@
           <t>ゾーン手前でのコイン投入判断が生まれる立ち回りの楽しさ</t>
         </is>
       </c>
+      <c r="I30" s="67" t="inlineStr">
+        <is>
+          <t>通常（高確ゾーン）</t>
+        </is>
+      </c>
     </row>
     <row r="31" ht="52" customHeight="1">
       <c r="A31" s="6" t="n"/>
@@ -1661,6 +1822,11 @@
           <t>「ここから打てば美味しい」という狙い目文化の醸成</t>
         </is>
       </c>
+      <c r="I31" s="67" t="inlineStr">
+        <is>
+          <t>通常（高確ゾーン）</t>
+        </is>
+      </c>
     </row>
     <row r="32" ht="52" customHeight="1">
       <c r="A32" s="7" t="n"/>
@@ -1689,6 +1855,11 @@
       <c r="H32" s="34" t="inlineStr">
         <is>
           <t>小役を引くたびにゾーンへの期待も高まる複合設計</t>
+        </is>
+      </c>
+      <c r="I32" s="67" t="inlineStr">
+        <is>
+          <t>通常（高確）</t>
         </is>
       </c>
     </row>
@@ -1742,6 +1913,11 @@
           <t>天井の存在がリスク許容度を高め「打ち切れる安心感」を提供</t>
         </is>
       </c>
+      <c r="I34" s="61" t="inlineStr">
+        <is>
+          <t>CZ（天井）</t>
+        </is>
+      </c>
     </row>
     <row r="35" ht="52" customHeight="1">
       <c r="A35" s="6" t="n"/>
@@ -1772,6 +1948,11 @@
           <t>天井の種類が多いほど狙い目が増えホール稼働向上に寄与</t>
         </is>
       </c>
+      <c r="I35" s="61" t="inlineStr">
+        <is>
+          <t>システム（天井）</t>
+        </is>
+      </c>
     </row>
     <row r="36" ht="52" customHeight="1">
       <c r="A36" s="7" t="n"/>
@@ -1800,6 +1981,11 @@
       <c r="H36" s="38" t="inlineStr">
         <is>
           <t>天井が動的に変化することで「今どこにいるか」の推測ゲームが生まれる</t>
+        </is>
+      </c>
+      <c r="I36" s="61" t="inlineStr">
+        <is>
+          <t>システム（天井）</t>
         </is>
       </c>
     </row>
